--- a/검수/AC000120253047CE9_또래지명_응답.xlsx
+++ b/검수/AC000120253047CE9_또래지명_응답.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\peer\검수\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qndba\peer\검수\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14B1767-AD02-466C-838C-C3943D44654D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A9BECA-1FCC-49C9-BBAD-8B171955F6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -555,11 +555,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E521"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -593,7 +592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -610,7 +609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -627,7 +626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -644,7 +643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -661,7 +660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -678,7 +677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -695,7 +694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -712,7 +711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -729,7 +728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -746,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -763,7 +762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -780,7 +779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -797,7 +796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -814,7 +813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -831,7 +830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -848,7 +847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -865,7 +864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -882,7 +881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -899,7 +898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -916,7 +915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -933,7 +932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -950,7 +949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -967,7 +966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -984,7 +983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1001,7 +1000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1018,7 +1017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1035,7 +1034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1052,7 +1051,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1086,7 +1085,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -1103,7 +1102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -1137,7 +1136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -1154,7 +1153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1171,7 +1170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1188,7 +1187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -1205,7 +1204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -1222,7 +1221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1256,7 +1255,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1272,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -1290,7 +1289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1307,7 +1306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1324,7 +1323,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -1341,7 +1340,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -1358,7 +1357,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -1392,7 +1391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -1426,7 +1425,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1443,7 +1442,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -1477,7 +1476,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -1511,7 +1510,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -1528,7 +1527,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -1545,7 +1544,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -1562,7 +1561,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>34</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>36</v>
       </c>
@@ -1596,7 +1595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -1613,7 +1612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>36</v>
       </c>
@@ -1630,7 +1629,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -1647,7 +1646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>9</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -1681,7 +1680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -1698,7 +1697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -1715,7 +1714,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>38</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>38</v>
       </c>
@@ -1783,7 +1782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>38</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -1834,7 +1833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -1885,7 +1884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -1902,7 +1901,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -1987,7 +1986,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -2004,7 +2003,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -2021,7 +2020,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -2055,7 +2054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>42</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>42</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>42</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>42</v>
       </c>
@@ -2157,7 +2156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>44</v>
       </c>
@@ -2174,7 +2173,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -2191,7 +2190,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>46</v>
       </c>
@@ -2208,7 +2207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>46</v>
       </c>
@@ -2225,7 +2224,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>46</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -2276,7 +2275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -2310,7 +2309,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>23</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>36</v>
       </c>
@@ -2344,7 +2343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>9</v>
       </c>
@@ -2361,7 +2360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -2378,7 +2377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -2429,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>20</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>20</v>
       </c>
@@ -2463,7 +2462,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>20</v>
       </c>
@@ -2480,7 +2479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>36</v>
       </c>
@@ -2497,7 +2496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>36</v>
       </c>
@@ -2514,7 +2513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>25</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>25</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>34</v>
       </c>
@@ -2616,7 +2615,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -2633,7 +2632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>36</v>
       </c>
@@ -2650,7 +2649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>36</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -2684,7 +2683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>9</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>25</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>23</v>
       </c>
@@ -2752,7 +2751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>23</v>
       </c>
@@ -2769,7 +2768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>23</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>23</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -2871,7 +2870,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>25</v>
       </c>
@@ -2888,7 +2887,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>27</v>
       </c>
@@ -2905,7 +2904,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>27</v>
       </c>
@@ -2922,7 +2921,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>27</v>
       </c>
@@ -2939,7 +2938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2973,7 +2972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -3007,7 +3006,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>8</v>
       </c>
@@ -3024,7 +3023,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>20</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>20</v>
       </c>
@@ -3058,7 +3057,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>20</v>
       </c>
@@ -3075,7 +3074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>20</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>22</v>
       </c>
@@ -3126,7 +3125,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>29</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -3245,7 +3244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>23</v>
       </c>
@@ -3262,7 +3261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>23</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>23</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>23</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>23</v>
       </c>
@@ -3330,7 +3329,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>23</v>
       </c>
@@ -3347,7 +3346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>32</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>32</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>32</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>32</v>
       </c>
@@ -3415,7 +3414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>32</v>
       </c>
@@ -3432,7 +3431,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>32</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>34</v>
       </c>
@@ -3466,7 +3465,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>34</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>34</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>34</v>
       </c>
@@ -3517,7 +3516,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>34</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -3551,7 +3550,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -3568,7 +3567,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>9</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -3619,7 +3618,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>25</v>
       </c>
@@ -3636,7 +3635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>38</v>
       </c>
@@ -3653,7 +3652,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>38</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>38</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -3704,7 +3703,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -3721,7 +3720,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -3738,7 +3737,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -3755,7 +3754,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>27</v>
       </c>
@@ -3772,7 +3771,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>27</v>
       </c>
@@ -3789,7 +3788,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>27</v>
       </c>
@@ -3806,7 +3805,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>14</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>14</v>
       </c>
@@ -3840,7 +3839,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>14</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>14</v>
       </c>
@@ -3874,7 +3873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>40</v>
       </c>
@@ -3891,7 +3890,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>40</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -3925,7 +3924,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -3942,7 +3941,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>40</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -3976,7 +3975,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -3993,7 +3992,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -4010,7 +4009,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -4044,7 +4043,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>42</v>
       </c>
@@ -4061,7 +4060,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>42</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>42</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>44</v>
       </c>
@@ -4112,7 +4111,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>44</v>
       </c>
@@ -4129,7 +4128,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>44</v>
       </c>
@@ -4146,7 +4145,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>44</v>
       </c>
@@ -4163,7 +4162,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>44</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>46</v>
       </c>
@@ -4197,7 +4196,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>46</v>
       </c>
@@ -4214,7 +4213,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>46</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>46</v>
       </c>
@@ -4248,7 +4247,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>46</v>
       </c>
@@ -4265,7 +4264,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -4299,7 +4298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -4316,7 +4315,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -4333,7 +4332,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -4350,7 +4349,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -4367,7 +4366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -4384,7 +4383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -4401,7 +4400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -4418,7 +4417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -4435,7 +4434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>23</v>
       </c>
@@ -4452,7 +4451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>23</v>
       </c>
@@ -4469,7 +4468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>23</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>23</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>36</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>27</v>
       </c>
@@ -4537,7 +4536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>40</v>
       </c>
@@ -4554,7 +4553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>44</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>44</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>44</v>
       </c>
@@ -4605,7 +4604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -4622,7 +4621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -4639,7 +4638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>36</v>
       </c>
@@ -4656,7 +4655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>36</v>
       </c>
@@ -4673,7 +4672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>36</v>
       </c>
@@ -4690,7 +4689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>36</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>9</v>
       </c>
@@ -4724,7 +4723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>38</v>
       </c>
@@ -4741,7 +4740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>38</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -4792,7 +4791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>8</v>
       </c>
@@ -4809,7 +4808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>8</v>
       </c>
@@ -4826,7 +4825,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>8</v>
       </c>
@@ -4843,7 +4842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>8</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>8</v>
       </c>
@@ -4877,7 +4876,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>8</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -4911,7 +4910,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -4928,7 +4927,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>20</v>
       </c>
@@ -4962,7 +4961,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>20</v>
       </c>
@@ -4979,7 +4978,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>20</v>
       </c>
@@ -4996,7 +4995,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -5013,7 +5012,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>20</v>
       </c>
@@ -5030,7 +5029,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>20</v>
       </c>
@@ -5047,7 +5046,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>22</v>
       </c>
@@ -5064,7 +5063,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>22</v>
       </c>
@@ -5081,7 +5080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>22</v>
       </c>
@@ -5098,7 +5097,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>22</v>
       </c>
@@ -5115,7 +5114,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>29</v>
       </c>
@@ -5132,7 +5131,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5148,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -5166,7 +5165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>29</v>
       </c>
@@ -5183,7 +5182,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>29</v>
       </c>
@@ -5200,7 +5199,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>29</v>
       </c>
@@ -5217,7 +5216,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>29</v>
       </c>
@@ -5234,7 +5233,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>29</v>
       </c>
@@ -5251,7 +5250,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -5268,7 +5267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -5285,7 +5284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>5</v>
       </c>
@@ -5302,7 +5301,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>5</v>
       </c>
@@ -5319,7 +5318,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>5</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -5353,7 +5352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>5</v>
       </c>
@@ -5370,7 +5369,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>23</v>
       </c>
@@ -5387,7 +5386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>23</v>
       </c>
@@ -5404,7 +5403,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>23</v>
       </c>
@@ -5421,7 +5420,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>23</v>
       </c>
@@ -5438,7 +5437,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>23</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>23</v>
       </c>
@@ -5472,7 +5471,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>23</v>
       </c>
@@ -5489,7 +5488,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>32</v>
       </c>
@@ -5506,7 +5505,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>32</v>
       </c>
@@ -5523,7 +5522,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>32</v>
       </c>
@@ -5540,7 +5539,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>32</v>
       </c>
@@ -5557,7 +5556,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>32</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>32</v>
       </c>
@@ -5591,7 +5590,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>34</v>
       </c>
@@ -5608,7 +5607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>34</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>34</v>
       </c>
@@ -5642,7 +5641,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>34</v>
       </c>
@@ -5659,7 +5658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>34</v>
       </c>
@@ -5676,7 +5675,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>34</v>
       </c>
@@ -5693,7 +5692,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>34</v>
       </c>
@@ -5710,7 +5709,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>34</v>
       </c>
@@ -5727,7 +5726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>36</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>36</v>
       </c>
@@ -5761,7 +5760,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>36</v>
       </c>
@@ -5778,7 +5777,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>36</v>
       </c>
@@ -5795,7 +5794,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>9</v>
       </c>
@@ -5812,7 +5811,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>9</v>
       </c>
@@ -5829,7 +5828,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>9</v>
       </c>
@@ -5846,7 +5845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>9</v>
       </c>
@@ -5863,7 +5862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>9</v>
       </c>
@@ -5880,7 +5879,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>25</v>
       </c>
@@ -5897,7 +5896,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>25</v>
       </c>
@@ -5914,7 +5913,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>25</v>
       </c>
@@ -5931,7 +5930,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>25</v>
       </c>
@@ -5948,7 +5947,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>12</v>
       </c>
@@ -5965,7 +5964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>12</v>
       </c>
@@ -5982,7 +5981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>12</v>
       </c>
@@ -5999,7 +5998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>12</v>
       </c>
@@ -6016,7 +6015,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>12</v>
       </c>
@@ -6033,7 +6032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>12</v>
       </c>
@@ -6050,7 +6049,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>27</v>
       </c>
@@ -6067,7 +6066,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>27</v>
       </c>
@@ -6084,7 +6083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>27</v>
       </c>
@@ -6101,7 +6100,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>27</v>
       </c>
@@ -6118,7 +6117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>27</v>
       </c>
@@ -6135,7 +6134,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>27</v>
       </c>
@@ -6152,7 +6151,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>27</v>
       </c>
@@ -6169,7 +6168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>14</v>
       </c>
@@ -6186,7 +6185,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>14</v>
       </c>
@@ -6203,7 +6202,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>14</v>
       </c>
@@ -6220,7 +6219,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>14</v>
       </c>
@@ -6237,7 +6236,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>14</v>
       </c>
@@ -6254,7 +6253,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>14</v>
       </c>
@@ -6271,7 +6270,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>14</v>
       </c>
@@ -6288,7 +6287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>14</v>
       </c>
@@ -6305,7 +6304,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -6322,7 +6321,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>40</v>
       </c>
@@ -6339,7 +6338,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>40</v>
       </c>
@@ -6356,7 +6355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>40</v>
       </c>
@@ -6373,7 +6372,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>40</v>
       </c>
@@ -6390,7 +6389,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>40</v>
       </c>
@@ -6407,7 +6406,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>40</v>
       </c>
@@ -6424,7 +6423,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>16</v>
       </c>
@@ -6441,7 +6440,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -6458,7 +6457,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>16</v>
       </c>
@@ -6475,7 +6474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>16</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>16</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>16</v>
       </c>
@@ -6526,7 +6525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>16</v>
       </c>
@@ -6543,7 +6542,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>16</v>
       </c>
@@ -6560,7 +6559,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>42</v>
       </c>
@@ -6577,7 +6576,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>42</v>
       </c>
@@ -6594,7 +6593,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>42</v>
       </c>
@@ -6611,7 +6610,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>42</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>42</v>
       </c>
@@ -6645,7 +6644,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>44</v>
       </c>
@@ -6662,7 +6661,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>44</v>
       </c>
@@ -6679,7 +6678,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>44</v>
       </c>
@@ -6696,7 +6695,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>44</v>
       </c>
@@ -6713,7 +6712,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>44</v>
       </c>
@@ -6730,7 +6729,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>44</v>
       </c>
@@ -6747,7 +6746,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>44</v>
       </c>
@@ -6764,7 +6763,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>44</v>
       </c>
@@ -6781,7 +6780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>46</v>
       </c>
@@ -6798,7 +6797,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>46</v>
       </c>
@@ -6815,7 +6814,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>46</v>
       </c>
@@ -6832,7 +6831,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>46</v>
       </c>
@@ -6849,7 +6848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>46</v>
       </c>
@@ -6866,7 +6865,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>46</v>
       </c>
@@ -6883,7 +6882,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>46</v>
       </c>
@@ -6900,7 +6899,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>18</v>
       </c>
@@ -6917,7 +6916,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>18</v>
       </c>
@@ -6934,7 +6933,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>18</v>
       </c>
@@ -6951,7 +6950,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>18</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>18</v>
       </c>
@@ -6985,7 +6984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>18</v>
       </c>
@@ -7002,7 +7001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>36</v>
       </c>
@@ -7019,7 +7018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>36</v>
       </c>
@@ -7036,7 +7035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>36</v>
       </c>
@@ -7053,7 +7052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>36</v>
       </c>
@@ -7070,7 +7069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>36</v>
       </c>
@@ -7087,7 +7086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>36</v>
       </c>
@@ -7104,7 +7103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>36</v>
       </c>
@@ -7121,7 +7120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>25</v>
       </c>
@@ -7138,7 +7137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>25</v>
       </c>
@@ -7155,7 +7154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>14</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>42</v>
       </c>
@@ -7189,7 +7188,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>18</v>
       </c>
@@ -7206,7 +7205,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>18</v>
       </c>
@@ -7223,7 +7222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>18</v>
       </c>
@@ -7240,7 +7239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>18</v>
       </c>
@@ -7257,7 +7256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>5</v>
       </c>
@@ -7274,7 +7273,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>34</v>
       </c>
@@ -7291,7 +7290,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>34</v>
       </c>
@@ -7308,7 +7307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>34</v>
       </c>
@@ -7325,7 +7324,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>9</v>
       </c>
@@ -7342,7 +7341,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>25</v>
       </c>
@@ -7359,7 +7358,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>25</v>
       </c>
@@ -7376,7 +7375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>25</v>
       </c>
@@ -7393,7 +7392,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>22</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>22</v>
       </c>
@@ -7427,7 +7426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>22</v>
       </c>
@@ -7444,7 +7443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>5</v>
       </c>
@@ -7461,7 +7460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>34</v>
       </c>
@@ -7478,7 +7477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>34</v>
       </c>
@@ -7495,7 +7494,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>36</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>36</v>
       </c>
@@ -7529,7 +7528,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>36</v>
       </c>
@@ -7546,7 +7545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>9</v>
       </c>
@@ -7563,7 +7562,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -7580,7 +7579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>5</v>
       </c>
@@ -7597,7 +7596,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>25</v>
       </c>
@@ -7614,7 +7613,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>25</v>
       </c>
@@ -7631,7 +7630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>25</v>
       </c>
@@ -7648,7 +7647,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -7665,7 +7664,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -7682,7 +7681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>42</v>
       </c>
@@ -7699,7 +7698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>42</v>
       </c>
@@ -7716,7 +7715,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>42</v>
       </c>
@@ -7733,7 +7732,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>44</v>
       </c>
@@ -7750,7 +7749,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>5</v>
       </c>
@@ -7767,7 +7766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>23</v>
       </c>
@@ -7784,7 +7783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>23</v>
       </c>
@@ -7801,7 +7800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>23</v>
       </c>
@@ -7818,7 +7817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>23</v>
       </c>
@@ -7835,7 +7834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>23</v>
       </c>
@@ -7852,7 +7851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>34</v>
       </c>
@@ -7869,7 +7868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>36</v>
       </c>
@@ -7886,7 +7885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>36</v>
       </c>
@@ -7903,7 +7902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>14</v>
       </c>
@@ -7920,7 +7919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>9</v>
       </c>
@@ -7937,7 +7936,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>9</v>
       </c>
@@ -7954,7 +7953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>9</v>
       </c>
@@ -7971,7 +7970,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>25</v>
       </c>
@@ -7988,7 +7987,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>25</v>
       </c>
@@ -8005,7 +8004,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>38</v>
       </c>
@@ -8022,7 +8021,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>38</v>
       </c>
@@ -8039,7 +8038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>38</v>
       </c>
@@ -8056,7 +8055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>38</v>
       </c>
@@ -8073,7 +8072,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>14</v>
       </c>
@@ -8090,7 +8089,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>23</v>
       </c>
@@ -8107,7 +8106,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>9</v>
       </c>
@@ -8124,7 +8123,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>25</v>
       </c>
@@ -8141,7 +8140,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>38</v>
       </c>
@@ -8158,7 +8157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -8175,7 +8174,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -8192,7 +8191,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -8226,7 +8225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -8243,7 +8242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -8260,7 +8259,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>18</v>
       </c>
@@ -8277,7 +8276,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>8</v>
       </c>
@@ -8294,7 +8293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>8</v>
       </c>
@@ -8311,7 +8310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>8</v>
       </c>
@@ -8328,7 +8327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>8</v>
       </c>
@@ -8345,7 +8344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>20</v>
       </c>
@@ -8362,7 +8361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>20</v>
       </c>
@@ -8379,7 +8378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>22</v>
       </c>
@@ -8396,7 +8395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>22</v>
       </c>
@@ -8413,7 +8412,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>29</v>
       </c>
@@ -8430,7 +8429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>29</v>
       </c>
@@ -8447,7 +8446,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>29</v>
       </c>
@@ -8464,7 +8463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>29</v>
       </c>
@@ -8481,7 +8480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>5</v>
       </c>
@@ -8498,7 +8497,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>5</v>
       </c>
@@ -8515,7 +8514,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>5</v>
       </c>
@@ -8532,7 +8531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>23</v>
       </c>
@@ -8549,7 +8548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>23</v>
       </c>
@@ -8566,7 +8565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>23</v>
       </c>
@@ -8583,7 +8582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>23</v>
       </c>
@@ -8600,7 +8599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>32</v>
       </c>
@@ -8617,7 +8616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>32</v>
       </c>
@@ -8634,7 +8633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>32</v>
       </c>
@@ -8651,7 +8650,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>34</v>
       </c>
@@ -8668,7 +8667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>36</v>
       </c>
@@ -8685,7 +8684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>36</v>
       </c>
@@ -8702,7 +8701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>9</v>
       </c>
@@ -8719,7 +8718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>9</v>
       </c>
@@ -8736,7 +8735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>25</v>
       </c>
@@ -8753,7 +8752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>25</v>
       </c>
@@ -8770,7 +8769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>25</v>
       </c>
@@ -8787,7 +8786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>38</v>
       </c>
@@ -8804,7 +8803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>38</v>
       </c>
@@ -8821,7 +8820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>38</v>
       </c>
@@ -8838,7 +8837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>38</v>
       </c>
@@ -8855,7 +8854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>12</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>12</v>
       </c>
@@ -8889,7 +8888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>12</v>
       </c>
@@ -8906,7 +8905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>12</v>
       </c>
@@ -8923,7 +8922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>27</v>
       </c>
@@ -8940,7 +8939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>27</v>
       </c>
@@ -8957,7 +8956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>27</v>
       </c>
@@ -8974,7 +8973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>27</v>
       </c>
@@ -8991,7 +8990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>14</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>14</v>
       </c>
@@ -9025,7 +9024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>14</v>
       </c>
@@ -9042,7 +9041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>14</v>
       </c>
@@ -9059,7 +9058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>40</v>
       </c>
@@ -9076,7 +9075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>40</v>
       </c>
@@ -9093,7 +9092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>40</v>
       </c>
@@ -9110,7 +9109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>16</v>
       </c>
@@ -9127,7 +9126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>16</v>
       </c>
@@ -9144,7 +9143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>16</v>
       </c>
@@ -9161,7 +9160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>16</v>
       </c>
@@ -9178,7 +9177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>16</v>
       </c>
@@ -9195,7 +9194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>16</v>
       </c>
@@ -9212,7 +9211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>16</v>
       </c>
@@ -9229,7 +9228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>42</v>
       </c>
@@ -9246,7 +9245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>42</v>
       </c>
@@ -9263,7 +9262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>42</v>
       </c>
@@ -9280,7 +9279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>44</v>
       </c>
@@ -9297,7 +9296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>44</v>
       </c>
@@ -9314,7 +9313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>44</v>
       </c>
@@ -9331,7 +9330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>46</v>
       </c>
@@ -9348,7 +9347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>46</v>
       </c>
@@ -9365,7 +9364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>46</v>
       </c>
@@ -9382,7 +9381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>46</v>
       </c>
@@ -9399,7 +9398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>46</v>
       </c>
@@ -9417,13 +9416,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E521" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E521" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9432,14 +9425,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{198D3C95-D640-4FA0-8A42-3519DCBF9B68}">
   <dimension ref="A2:L39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <f>COUNTIF($L$3:$L$39,A2)</f>
+        <f t="shared" ref="B2:B12" si="0">COUNTIF($L$3:$L$39,A2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -9458,12 +9451,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <f>COUNTIF($L$3:$L$39,A3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H3" t="s">
@@ -9482,12 +9475,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
-        <f>COUNTIF($L$3:$L$39,A4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H4" t="s">
@@ -9506,12 +9499,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <f>COUNTIF($L$3:$L$39,A5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H5" t="s">
@@ -9530,12 +9523,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <f>COUNTIF($L$3:$L$39,A6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" t="s">
@@ -9554,12 +9547,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7">
-        <f>COUNTIF($L$3:$L$39,A7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H7" t="s">
@@ -9578,12 +9571,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
-        <f>COUNTIF($L$3:$L$39,A8)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H8" t="s">
@@ -9602,12 +9595,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <f>COUNTIF($L$3:$L$39,A9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" t="s">
@@ -9626,12 +9619,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10">
-        <f>COUNTIF($L$3:$L$39,A10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H10" t="s">
@@ -9650,12 +9643,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>27</v>
       </c>
       <c r="B11">
-        <f>COUNTIF($L$3:$L$39,A11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H11" t="s">
@@ -9674,12 +9667,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12">
-        <f>COUNTIF($L$3:$L$39,A12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H12" t="s">
@@ -9698,12 +9691,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13:B22" si="0">COUNTIF($L$3:$L$39,A13)</f>
+        <f t="shared" ref="B13:B22" si="1">COUNTIF($L$3:$L$39,A13)</f>
         <v>1</v>
       </c>
       <c r="H13" t="s">
@@ -9722,12 +9715,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>32</v>
       </c>
       <c r="B14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" t="s">
@@ -9746,12 +9739,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>34</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H15" t="s">
@@ -9770,12 +9763,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>36</v>
       </c>
       <c r="B16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="H16" t="s">
@@ -9794,12 +9787,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="B17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" t="s">
@@ -9818,12 +9811,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>40</v>
       </c>
       <c r="B18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" t="s">
@@ -9842,12 +9835,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H19" t="s">
@@ -9866,12 +9859,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>44</v>
       </c>
       <c r="B20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H20" t="s">
@@ -9890,12 +9883,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H21" t="s">
@@ -9914,12 +9907,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H22" t="s">
@@ -9938,7 +9931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
         <v>29</v>
       </c>
@@ -9955,7 +9948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
         <v>5</v>
       </c>
@@ -9972,7 +9965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
         <v>23</v>
       </c>
@@ -9989,7 +9982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
         <v>32</v>
       </c>
@@ -10006,7 +9999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
         <v>34</v>
       </c>
@@ -10023,7 +10016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
         <v>36</v>
       </c>
@@ -10040,7 +10033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
         <v>9</v>
       </c>
@@ -10057,7 +10050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
         <v>25</v>
       </c>
@@ -10074,7 +10067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
         <v>38</v>
       </c>
@@ -10091,7 +10084,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
         <v>12</v>
       </c>
@@ -10108,7 +10101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
         <v>27</v>
       </c>
@@ -10125,7 +10118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
         <v>14</v>
       </c>
@@ -10142,7 +10135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H35" t="s">
         <v>40</v>
       </c>
@@ -10159,7 +10152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H36" t="s">
         <v>16</v>
       </c>
@@ -10176,7 +10169,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H37" t="s">
         <v>42</v>
       </c>
@@ -10193,7 +10186,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H38" t="s">
         <v>44</v>
       </c>
@@ -10210,7 +10203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="8:12" x14ac:dyDescent="0.45">
       <c r="H39" t="s">
         <v>46</v>
       </c>
